--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/03_workforce_roles.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/03_workforce_roles.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rff15511aa18a4fbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R4a99cc7e3c414032"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R3b16f455114e4d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R6c12f0e629a24540"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rd5f72d411ff147f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rf8e35b26225a4734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R48ab6ff27a734d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R4e43b7f7f9134ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R6dc94f2767034ac5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R9858dbabb1534929"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R7bbe41673e4a4e4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R7b7f0cb560674cbd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,7 +624,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f19ddc6fd6e4be3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea1e52fb7d7e48c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -779,7 +779,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K6" s="78" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Validate Executive Office Product / Process Owner (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for workforce roles.</x:v>
       </x:c>
       <x:c r="L6" s="78" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -823,7 +823,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K7" s="79" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm Executive Office Analyst / Steward (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L7" s="79" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -867,7 +867,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Attach client evidence for Retail Deposits and Branch Operations Product / Process Owner (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="L8" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -911,7 +911,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Reconcile Retail Deposits and Branch Operations Analyst / Steward (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="L9" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -955,7 +955,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending and Treasury Product / Process Owner (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="L10" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -999,7 +999,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Validate Commercial Lending and Treasury Analyst / Steward (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for workforce roles.</x:v>
       </x:c>
       <x:c r="L11" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1043,7 +1043,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Confirm Cards Operations Product / Process Owner (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L12" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1087,7 +1087,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Attach client evidence for Cards Operations Analyst / Steward (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="L13" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1131,7 +1131,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Reconcile Payments Operations Product / Process Owner (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="L14" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1175,7 +1175,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations Analyst / Steward (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="L15" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1219,7 +1219,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Validate Consumer Lending Operations Product / Process Owner (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for workforce roles.</x:v>
       </x:c>
       <x:c r="L16" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1263,7 +1263,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm Consumer Lending Operations Analyst / Steward (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L17" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1307,7 +1307,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Attach client evidence for Wealth Advisory and Brokerage Product / Process Owner (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="L18" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1351,7 +1351,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Reconcile Wealth Advisory and Brokerage Analyst / Steward (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="L19" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1395,7 +1395,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Validate Fraud and Risk Operations Product / Process Owner (record 15) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="L20" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1439,7 +1439,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Validate Fraud and Risk Operations Analyst / Steward (record 16) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="L21" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1483,7 +1483,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Confirm Compliance and Model Risk Management Product / Process Owner (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L22" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1527,7 +1527,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Attach client evidence for Compliance and Model Risk Management Analyst / Steward (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="L23" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1571,7 +1571,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Reconcile Contact Center and Servicing Product / Process Owner (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="L24" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1615,7 +1615,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing Analyst / Steward (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="L25" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding Product / Process Owner (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for workforce roles.</x:v>
       </x:c>
       <x:c r="L26" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1703,7 +1703,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm Digital Account Opening and Onboarding Analyst / Steward (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L27" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1747,7 +1747,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Attach client evidence for Core Banking Modernization Product / Process Owner (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="L28" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1791,7 +1791,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Reconcile Core Banking Modernization Analyst / Steward (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="L29" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1835,7 +1835,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer 360 Data Product Product / Process Owner (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="L30" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1879,7 +1879,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Validate Customer 360 Data Product Analyst / Steward (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for workforce roles.</x:v>
       </x:c>
       <x:c r="L31" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -1923,7 +1923,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Confirm Retail Banking Analytics Product / Process Owner (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L32" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -1967,7 +1967,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics Analyst / Steward (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="L33" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2011,7 +2011,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics Product / Process Owner (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="L34" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -2055,7 +2055,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics Analyst / Steward (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="L35" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2099,7 +2099,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Validate Payments and Settlement Analytics Product / Process Owner (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for workforce roles.</x:v>
       </x:c>
       <x:c r="L36" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -2143,7 +2143,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm Payments and Settlement Analytics Analyst / Steward (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L37" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2187,7 +2187,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Product / Process Owner (record 33) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="L38" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -2231,7 +2231,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Analyst / Steward (record 34) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="L39" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2275,7 +2275,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cloud Data Platform Product / Process Owner (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="L40" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -2319,7 +2319,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Validate Cloud Data Platform Analyst / Steward (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for workforce roles.</x:v>
       </x:c>
       <x:c r="L41" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2363,7 +2363,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K42" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline Product / Process Owner (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L42" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -2407,7 +2407,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline Analyst / Steward (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="L43" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2451,7 +2451,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K44" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization Product / Process Owner (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="L44" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -2495,7 +2495,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K45" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization Analyst / Steward (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="L45" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2539,7 +2539,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K46" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Validate Infrastructure and CMDB Product / Process Owner (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for workforce roles.</x:v>
       </x:c>
       <x:c r="L46" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -2583,7 +2583,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K47" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Confirm Infrastructure and CMDB Analyst / Steward (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this workforce roles record is used downstream.</x:v>
       </x:c>
       <x:c r="L47" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2627,7 +2627,7 @@
         <x:v>Domain operations, data literacy, controls, vendor coordination, stakeholder management</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>Named owner and FTE allocation require validation.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations Product / Process Owner (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="L48" t="str">
         <x:v>Approves whether AI assistance can be piloted and what human review controls are required.</x:v>
@@ -2671,7 +2671,7 @@
         <x:v>SQL/reporting, process knowledge, data quality triage, privacy/security awareness</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>Exact analyst population, contractor split, and managed service handoff need validation.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations Analyst / Steward (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="L49" t="str">
         <x:v>High - likely consumer of context extracts, agent assist, summarization, and analytics automation.</x:v>
@@ -2698,7 +2698,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R974434c1894544ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13028e1ac83b4c59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2773,7 +2773,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb36b8ab6724e83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec384a16c1764ca0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2947,7 +2947,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20201d05130448ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c902cea7c9940d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3009,7 +3009,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31a3863a6f2d46ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcf8e93c4f5c49f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3119,7 +3119,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac373b8366a24f75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79a1f2995ca84ec1"/>
   </x:tableParts>
 </x:worksheet>
 </file>